--- a/results/semis_acceleration_screen.xlsx
+++ b/results/semis_acceleration_screen.xlsx
@@ -33395,7 +33395,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -33425,7 +33425,7 @@
         <v>0.1060738722962675</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="M20" s="5" t="b">
         <v>0</v>
@@ -33444,7 +33444,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -33474,7 +33474,7 @@
         <v>0.1060738722962675</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M21" s="5" t="b">
         <v>0</v>
@@ -34762,12 +34762,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -34797,7 +34797,7 @@
         <v>1</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M48" s="5" t="b">
         <v>0</v>
@@ -34811,12 +34811,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -34846,7 +34846,7 @@
         <v>1</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M49" s="5" t="b">
         <v>0</v>
@@ -34958,12 +34958,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -34993,10 +34993,10 @@
         <v>1</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="M52" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -35007,12 +35007,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -35042,10 +35042,10 @@
         <v>1</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="M53" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -35056,12 +35056,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -35091,7 +35091,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="M54" s="5" t="b">
         <v>0</v>
@@ -35105,12 +35105,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="M55" s="5" t="b">
         <v>0</v>
@@ -35154,12 +35154,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -35189,7 +35189,7 @@
         <v>1</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M56" s="5" t="b">
         <v>0</v>
@@ -35203,12 +35203,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -35238,7 +35238,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M57" s="5" t="b">
         <v>0</v>
@@ -35742,12 +35742,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -35777,7 +35777,7 @@
         <v>1</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M68" s="5" t="b">
         <v>0</v>
@@ -35791,12 +35791,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -35826,7 +35826,7 @@
         <v>1</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M69" s="5" t="b">
         <v>0</v>
@@ -37332,12 +37332,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -37364,7 +37364,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="M12" s="5" t="b">
         <v>0</v>
@@ -37378,12 +37378,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -37410,7 +37410,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M13" s="5" t="b">
         <v>0</v>
@@ -39708,7 +39708,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -39755,7 +39755,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -40238,7 +40238,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -40268,7 +40268,7 @@
         <v>0.1060738722962675</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="M7" s="5" t="b">
         <v>0</v>
@@ -40287,7 +40287,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -40317,7 +40317,7 @@
         <v>0.1060738722962675</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M8" s="5" t="b">
         <v>0</v>
@@ -42161,7 +42161,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -42171,32 +42171,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>26</v>
+        <v>3.1</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.0006955963400931029</v>
-      </c>
-      <c r="AP18" s="4" t="n">
-        <v>-0.2116666666666667</v>
-      </c>
-      <c r="AQ18" s="4" t="n">
-        <v>-0.3116666666666666</v>
+        <v>0.005165504428170329</v>
       </c>
       <c r="AR18" s="4" t="n">
-        <v>-0.9951219512195122</v>
-      </c>
-      <c r="AS18" s="4" t="n">
-        <v>-0.9660574412532636</v>
+        <v>-0.625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -42206,23 +42197,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3.1</v>
+        <v>26</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.005165504428170329</v>
+        <v>0.0006955963400931029</v>
+      </c>
+      <c r="AP19" s="4" t="n">
+        <v>-0.2116666666666667</v>
+      </c>
+      <c r="AQ19" s="4" t="n">
+        <v>-0.3116666666666666</v>
       </c>
       <c r="AR19" s="4" t="n">
-        <v>-0.625</v>
+        <v>-0.9951219512195122</v>
+      </c>
+      <c r="AS19" s="4" t="n">
+        <v>-0.9660574412532636</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -42232,20 +42232,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>0.004645855407938707</v>
+      </c>
+      <c r="AP20" s="4" t="n">
+        <v>-0.5321428571428571</v>
+      </c>
+      <c r="AT20" s="4" t="n">
+        <v>-0.5648854961832062</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NVMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -42255,32 +42261,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>46500</v>
+        <v>72.41200000000001</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.3200000000000001</v>
+        <v>-0.4338770388958595</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.143939393939394</v>
+        <v>1.090868794326241</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>0.9139072847682119</v>
+        <v>2.251642993428026</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.5709342560553634</v>
+        <v>0.9913287260399009</v>
       </c>
       <c r="AL21" s="4" t="n">
-        <v>-0.008810572687224627</v>
+        <v>0.3743902039747242</v>
       </c>
       <c r="AP21" s="4" t="n">
-        <v>-0.0377777777777778</v>
+        <v>0.8224307970841869</v>
       </c>
       <c r="AT21" s="4" t="n">
-        <v>0.07390300230946889</v>
+        <v>-0.0534626545711222</v>
       </c>
     </row>
     <row r="22">
@@ -42296,38 +42302,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>19372.6</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0.1937413427329455</v>
+        <v>16006.3</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.4526315789473683</v>
+        <v>0.1298039215686273</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.4513070567519979</v>
+        <v>0.4615295614948514</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.3052029864675689</v>
+        <v>0.565151994933502</v>
       </c>
       <c r="AD22" s="4" t="n">
-        <v>0.995119858422266</v>
+        <v>1.006777603560771</v>
       </c>
       <c r="AH22" s="4" t="n">
-        <v>0.5904541748425307</v>
+        <v>0.572865208186309</v>
       </c>
       <c r="AL22" s="4" t="n">
-        <v>-0.08362392892754744</v>
+        <v>-0.08332665651790727</v>
       </c>
       <c r="AP22" s="4" t="n">
-        <v>0.1186303138351827</v>
+        <v>0.09875010925618377</v>
       </c>
       <c r="AT22" s="4" t="n">
-        <v>0.06465086116881524</v>
+        <v>0.2732920736945939</v>
       </c>
     </row>
     <row r="23">
@@ -42380,7 +42383,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TSEM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -42390,44 +42393,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>25.581</v>
-      </c>
-      <c r="AB24" s="4" t="n">
-        <v>1.319101123595506</v>
+        <v>46500</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="Z24" s="4" t="n">
+        <v>0.143939393939394</v>
       </c>
       <c r="AD24" s="4" t="n">
-        <v>2.988431235663708</v>
-      </c>
-      <c r="AF24" s="4" t="n">
-        <v>0.9702162382700936</v>
+        <v>0.9139072847682119</v>
       </c>
       <c r="AH24" s="4" t="n">
-        <v>-0.0270304060812161</v>
-      </c>
-      <c r="AJ24" s="4" t="n">
-        <v>-0.4201180368606336</v>
+        <v>0.5709342560553634</v>
       </c>
       <c r="AL24" s="4" t="n">
-        <v>-0.5266634113746755</v>
-      </c>
-      <c r="AN24" s="4" t="n">
-        <v>0.07079725024551364</v>
+        <v>-0.008810572687224627</v>
       </c>
       <c r="AP24" s="4" t="n">
-        <v>0.175751981756977</v>
+        <v>-0.0377777777777778</v>
       </c>
       <c r="AT24" s="4" t="n">
-        <v>0.1812976217963518</v>
+        <v>0.07390300230946889</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -42441,34 +42438,40 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>72.41200000000001</v>
+        <v>19372.6</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>0.1937413427329455</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>0.4526315789473683</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4338770388958595</v>
+        <v>0.4513070567519979</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.090868794326241</v>
+        <v>0.3052029864675689</v>
       </c>
       <c r="AD25" s="4" t="n">
-        <v>2.251642993428026</v>
+        <v>0.995119858422266</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.9913287260399009</v>
+        <v>0.5904541748425307</v>
       </c>
       <c r="AL25" s="4" t="n">
-        <v>0.3743902039747242</v>
+        <v>-0.08362392892754744</v>
       </c>
       <c r="AP25" s="4" t="n">
-        <v>0.8224307970841869</v>
+        <v>0.1186303138351827</v>
       </c>
       <c r="AT25" s="4" t="n">
-        <v>-0.0534626545711222</v>
+        <v>0.06465086116881524</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -42482,37 +42485,16 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>67.163</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>-0.6144764853880395</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>-0.4337349397590362</v>
-      </c>
-      <c r="Z26" s="4" t="n">
-        <v>1.090868794326241</v>
-      </c>
-      <c r="AD26" s="4" t="n">
-        <v>2.251642993428026</v>
-      </c>
-      <c r="AH26" s="4" t="n">
-        <v>0.9913287260399009</v>
-      </c>
-      <c r="AL26" s="4" t="n">
-        <v>0.3743902039747242</v>
-      </c>
-      <c r="AP26" s="4" t="n">
-        <v>0.7362904378483965</v>
-      </c>
-      <c r="AT26" s="4" t="n">
-        <v>-0.0785198803611119</v>
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>TSEM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -42522,26 +42504,44 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.004645855407938707</v>
+        <v>25.581</v>
+      </c>
+      <c r="AB27" s="4" t="n">
+        <v>1.319101123595506</v>
+      </c>
+      <c r="AD27" s="4" t="n">
+        <v>2.988431235663708</v>
+      </c>
+      <c r="AF27" s="4" t="n">
+        <v>0.9702162382700936</v>
+      </c>
+      <c r="AH27" s="4" t="n">
+        <v>-0.0270304060812161</v>
+      </c>
+      <c r="AJ27" s="4" t="n">
+        <v>-0.4201180368606336</v>
+      </c>
+      <c r="AL27" s="4" t="n">
+        <v>-0.5266634113746755</v>
+      </c>
+      <c r="AN27" s="4" t="n">
+        <v>0.07079725024551364</v>
       </c>
       <c r="AP27" s="4" t="n">
-        <v>-0.5321428571428571</v>
+        <v>0.175751981756977</v>
       </c>
       <c r="AT27" s="4" t="n">
-        <v>-0.5648854961832062</v>
+        <v>0.1812976217963518</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NVMI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -42555,31 +42555,31 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>16006.3</v>
+        <v>67.163</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.1298039215686273</v>
+        <v>-0.6144764853880395</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.4615295614948514</v>
+        <v>-0.4337349397590362</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.565151994933502</v>
+        <v>1.090868794326241</v>
       </c>
       <c r="AD28" s="4" t="n">
-        <v>1.006777603560771</v>
+        <v>2.251642993428026</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.572865208186309</v>
+        <v>0.9913287260399009</v>
       </c>
       <c r="AL28" s="4" t="n">
-        <v>-0.08332665651790727</v>
+        <v>0.3743902039747242</v>
       </c>
       <c r="AP28" s="4" t="n">
-        <v>0.09875010925618377</v>
+        <v>0.7362904378483965</v>
       </c>
       <c r="AT28" s="4" t="n">
-        <v>0.2732920736945939</v>
+        <v>-0.0785198803611119</v>
       </c>
     </row>
     <row r="29">
@@ -42595,41 +42595,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>8000</v>
+        <v>1020.172</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.447017543098061</v>
+        <v>0.1845258476221794</v>
       </c>
       <c r="AM29" s="4" t="n">
-        <v>0.1111111111111112</v>
+        <v>-0.09363152661997831</v>
       </c>
       <c r="AN29" s="4" t="n">
-        <v>0.1320754716981132</v>
+        <v>-0.01982895372094629</v>
       </c>
       <c r="AO29" s="4" t="n">
-        <v>0.03703703703703698</v>
+        <v>0.04404349556107845</v>
       </c>
       <c r="AP29" s="4" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1160094508184382</v>
       </c>
       <c r="AQ29" s="4" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.126757394214813</v>
       </c>
       <c r="AR29" s="4" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.1524013546671252</v>
       </c>
       <c r="AS29" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1312911186779546</v>
       </c>
       <c r="AT29" s="4" t="n">
-        <v>0.1470588235294117</v>
+        <v>0.09600378145888788</v>
       </c>
       <c r="AU29" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2126541713025039</v>
       </c>
     </row>
     <row r="30">
@@ -42645,47 +42645,47 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>25.706</v>
+        <v>30.9</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.03564559630037925</v>
+        <v>0.04284793144330969</v>
       </c>
       <c r="AM30" s="4" t="n">
-        <v>-0.2422664489651826</v>
+        <v>-0.2701612903225806</v>
       </c>
       <c r="AN30" s="4" t="n">
-        <v>-0.09743646044903109</v>
+        <v>-0.3482758620689655</v>
       </c>
       <c r="AO30" s="4" t="n">
-        <v>0.05508289703315894</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="AP30" s="4" t="n">
-        <v>0.2082941664362732</v>
+        <v>0.3316062176165802</v>
       </c>
       <c r="AQ30" s="4" t="n">
-        <v>0.2816958825927436</v>
+        <v>0.4309392265193368</v>
       </c>
       <c r="AR30" s="4" t="n">
-        <v>0.2522807444349835</v>
+        <v>0.6560846560846563</v>
       </c>
       <c r="AS30" s="4" t="n">
-        <v>0.314948826630828</v>
+        <v>-0.1524822695035462</v>
       </c>
       <c r="AT30" s="4" t="n">
-        <v>0.4461376533040453</v>
+        <v>0.350194552529183</v>
       </c>
       <c r="AU30" s="4" t="n">
-        <v>0.1680298073427844</v>
+        <v>0.1930501930501931</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RMBS</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -42695,47 +42695,47 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>23.719</v>
+        <v>8000</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.03289029404219621</v>
+        <v>1.447017543098061</v>
       </c>
       <c r="AM31" s="4" t="n">
-        <v>-0.2133262976110525</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AN31" s="4" t="n">
-        <v>-0.08308004052684903</v>
+        <v>0.1320754716981132</v>
       </c>
       <c r="AO31" s="4" t="n">
-        <v>0.0541268113866773</v>
+        <v>0.03703703703703698</v>
       </c>
       <c r="AP31" s="4" t="n">
-        <v>0.1443109296843557</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AQ31" s="4" t="n">
-        <v>0.2400756143667295</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="AR31" s="4" t="n">
-        <v>0.224894377640559</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="AS31" s="4" t="n">
-        <v>0.2936861551836558</v>
+        <v>0.25</v>
       </c>
       <c r="AT31" s="4" t="n">
-        <v>0.5063055820730544</v>
+        <v>0.1470588235294117</v>
       </c>
       <c r="AU31" s="4" t="n">
-        <v>0.1663552321007082</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RMBS</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -42745,47 +42745,47 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>30.9</v>
+        <v>873.598</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.04284793144330969</v>
+        <v>0.1580139539519225</v>
       </c>
       <c r="AM32" s="4" t="n">
-        <v>-0.2701612903225806</v>
+        <v>-0.08543270950549453</v>
       </c>
       <c r="AN32" s="4" t="n">
-        <v>-0.3482758620689655</v>
+        <v>-0.01121241219129443</v>
       </c>
       <c r="AO32" s="4" t="n">
-        <v>0.4099999999999999</v>
+        <v>0.04794971061981723</v>
       </c>
       <c r="AP32" s="4" t="n">
-        <v>0.3316062176165802</v>
+        <v>0.1088517106149554</v>
       </c>
       <c r="AQ32" s="4" t="n">
-        <v>0.4309392265193368</v>
+        <v>0.1075484970316603</v>
       </c>
       <c r="AR32" s="4" t="n">
-        <v>0.6560846560846563</v>
+        <v>0.07564272220077273</v>
       </c>
       <c r="AS32" s="4" t="n">
-        <v>-0.1524822695035462</v>
+        <v>0.1109830963148934</v>
       </c>
       <c r="AT32" s="4" t="n">
-        <v>0.350194552529183</v>
+        <v>0.05562961325607207</v>
       </c>
       <c r="AU32" s="4" t="n">
-        <v>0.1930501930501931</v>
+        <v>0.1957759010088012</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>RMBS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -42799,43 +42799,43 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>873.598</v>
+        <v>23.719</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.1580139539519225</v>
+        <v>0.03289029404219621</v>
       </c>
       <c r="AM33" s="4" t="n">
-        <v>-0.08543270950549453</v>
+        <v>-0.2133262976110525</v>
       </c>
       <c r="AN33" s="4" t="n">
-        <v>-0.01121241219129443</v>
+        <v>-0.08308004052684903</v>
       </c>
       <c r="AO33" s="4" t="n">
-        <v>0.04794971061981723</v>
+        <v>0.0541268113866773</v>
       </c>
       <c r="AP33" s="4" t="n">
-        <v>0.1088517106149554</v>
+        <v>0.1443109296843557</v>
       </c>
       <c r="AQ33" s="4" t="n">
-        <v>0.1075484970316603</v>
+        <v>0.2400756143667295</v>
       </c>
       <c r="AR33" s="4" t="n">
-        <v>0.07564272220077273</v>
+        <v>0.224894377640559</v>
       </c>
       <c r="AS33" s="4" t="n">
-        <v>0.1109830963148934</v>
+        <v>0.2936861551836558</v>
       </c>
       <c r="AT33" s="4" t="n">
-        <v>0.05562961325607207</v>
+        <v>0.5063055820730544</v>
       </c>
       <c r="AU33" s="4" t="n">
-        <v>0.1957759010088012</v>
+        <v>0.1663552321007082</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>RMBS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -42849,43 +42849,43 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1020.172</v>
+        <v>25.706</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.1845258476221794</v>
+        <v>0.03564559630037925</v>
       </c>
       <c r="AM34" s="4" t="n">
-        <v>-0.09363152661997831</v>
+        <v>-0.2422664489651826</v>
       </c>
       <c r="AN34" s="4" t="n">
-        <v>-0.01982895372094629</v>
+        <v>-0.09743646044903109</v>
       </c>
       <c r="AO34" s="4" t="n">
-        <v>0.04404349556107845</v>
+        <v>0.05508289703315894</v>
       </c>
       <c r="AP34" s="4" t="n">
-        <v>0.1160094508184382</v>
+        <v>0.2082941664362732</v>
       </c>
       <c r="AQ34" s="4" t="n">
-        <v>0.126757394214813</v>
+        <v>0.2816958825927436</v>
       </c>
       <c r="AR34" s="4" t="n">
-        <v>0.1524013546671252</v>
+        <v>0.2522807444349835</v>
       </c>
       <c r="AS34" s="4" t="n">
-        <v>0.1312911186779546</v>
+        <v>0.314948826630828</v>
       </c>
       <c r="AT34" s="4" t="n">
-        <v>0.09600378145888788</v>
+        <v>0.4461376533040453</v>
       </c>
       <c r="AU34" s="4" t="n">
-        <v>0.2126541713025039</v>
+        <v>0.1680298073427844</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -42899,43 +42899,40 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>222</v>
+        <v>2122.6</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.005374651979179276</v>
-      </c>
-      <c r="AN35" s="4" t="n">
-        <v>-0.7226277372262774</v>
+        <v>0.4116757176105508</v>
       </c>
       <c r="AO35" s="4" t="n">
-        <v>-0.5520833333333333</v>
+        <v>-0.01221785048664314</v>
       </c>
       <c r="AP35" s="4" t="n">
-        <v>-0.3795620437956204</v>
+        <v>-0.0445540484997945</v>
       </c>
       <c r="AQ35" s="4" t="n">
-        <v>-0.3451327433628318</v>
+        <v>-0.1042102720978909</v>
       </c>
       <c r="AR35" s="4" t="n">
-        <v>1.868421052631579</v>
+        <v>0.02979979702924629</v>
       </c>
       <c r="AS35" s="4" t="n">
-        <v>2.244186046511628</v>
+        <v>-0.05832285115303981</v>
       </c>
       <c r="AT35" s="4" t="n">
-        <v>2.705882352941177</v>
+        <v>-0.07584100490406942</v>
       </c>
       <c r="AU35" s="4" t="n">
-        <v>2.567567567567568</v>
+        <v>-0.06924286677151192</v>
       </c>
       <c r="AV35" s="4" t="n">
-        <v>0.0183486238532109</v>
+        <v>-0.04918473391865263</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -42945,47 +42942,44 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2433.996</v>
+        <v>939</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.1047659999767569</v>
-      </c>
-      <c r="AN36" s="4" t="n">
-        <v>-0.155781005241288</v>
+        <v>0.1821179208688906</v>
       </c>
       <c r="AO36" s="4" t="n">
-        <v>0.2109477552387031</v>
+        <v>-0.103112840466926</v>
       </c>
       <c r="AP36" s="4" t="n">
-        <v>0.05371039250141574</v>
+        <v>-0.03239289446186</v>
       </c>
       <c r="AQ36" s="4" t="n">
-        <v>0.1518078638137978</v>
+        <v>-0.004371584699453535</v>
       </c>
       <c r="AR36" s="4" t="n">
-        <v>0.7279362669148413</v>
+        <v>0.0844155844155845</v>
       </c>
       <c r="AS36" s="4" t="n">
-        <v>0.3527820373094264</v>
+        <v>0.1171366594360086</v>
       </c>
       <c r="AT36" s="4" t="n">
-        <v>0.1075019688915142</v>
+        <v>0.1349892008639308</v>
       </c>
       <c r="AU36" s="4" t="n">
-        <v>0.104516534568482</v>
+        <v>0.1481888035126235</v>
       </c>
       <c r="AV36" s="4" t="n">
-        <v>-0.09215127306038395</v>
+        <v>-0.06287425149700598</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -42999,40 +42993,40 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2279.168</v>
+        <v>200</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.09810176953249926</v>
-      </c>
-      <c r="AN37" s="4" t="n">
-        <v>-0.1636600773586453</v>
+        <v>0.03878975950349108</v>
+      </c>
+      <c r="AO37" s="4" t="n">
+        <v>-0.2430555555555556</v>
       </c>
       <c r="AP37" s="4" t="n">
-        <v>0.07526011528454424</v>
+        <v>-0.2107623318385651</v>
       </c>
       <c r="AQ37" s="4" t="n">
-        <v>0.1751889984160906</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="AR37" s="4" t="n">
-        <v>0.8095460441351663</v>
+        <v>0.2392344497607655</v>
       </c>
       <c r="AS37" s="4" t="n">
-        <v>0.3660370151472527</v>
+        <v>0.3577981651376148</v>
       </c>
       <c r="AT37" s="4" t="n">
-        <v>0.1228434358130872</v>
+        <v>0.8806818181818181</v>
       </c>
       <c r="AU37" s="4" t="n">
-        <v>0.1109991345873407</v>
+        <v>0.4066985645933014</v>
       </c>
       <c r="AV37" s="4" t="n">
-        <v>-0.1116225044240199</v>
+        <v>-0.2277992277992278</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -43042,44 +43036,47 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>939</v>
+        <v>174.2</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.1821179208688906</v>
+        <v>0.03400816039669679</v>
+      </c>
+      <c r="AN38" s="4" t="n">
+        <v>0.728768926925609</v>
       </c>
       <c r="AO38" s="4" t="n">
-        <v>-0.103112840466926</v>
+        <v>0.3705179282868527</v>
       </c>
       <c r="AP38" s="4" t="n">
-        <v>-0.03239289446186</v>
+        <v>0.1712598425196852</v>
       </c>
       <c r="AQ38" s="4" t="n">
-        <v>-0.004371584699453535</v>
+        <v>-0.1848739495798319</v>
       </c>
       <c r="AR38" s="4" t="n">
-        <v>0.0844155844155845</v>
+        <v>-0.3903274942878904</v>
       </c>
       <c r="AS38" s="4" t="n">
-        <v>0.1171366594360086</v>
+        <v>-0.3355481727574751</v>
       </c>
       <c r="AT38" s="4" t="n">
-        <v>0.1349892008639308</v>
+        <v>-0.3151260504201681</v>
       </c>
       <c r="AU38" s="4" t="n">
-        <v>0.1481888035126235</v>
+        <v>-0.1602624179943768</v>
       </c>
       <c r="AV38" s="4" t="n">
-        <v>-0.06287425149700598</v>
+        <v>0.08806995627732661</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -43093,40 +43090,13 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.03878975950349108</v>
-      </c>
-      <c r="AO39" s="4" t="n">
-        <v>-0.2430555555555556</v>
-      </c>
-      <c r="AP39" s="4" t="n">
-        <v>-0.2107623318385651</v>
-      </c>
-      <c r="AQ39" s="4" t="n">
-        <v>0.05555555555555558</v>
-      </c>
-      <c r="AR39" s="4" t="n">
-        <v>0.2392344497607655</v>
-      </c>
-      <c r="AS39" s="4" t="n">
-        <v>0.3577981651376148</v>
-      </c>
-      <c r="AT39" s="4" t="n">
-        <v>0.8806818181818181</v>
-      </c>
-      <c r="AU39" s="4" t="n">
-        <v>0.4066985645933014</v>
-      </c>
-      <c r="AV39" s="4" t="n">
-        <v>-0.2277992277992278</v>
+        <v>173.735</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -43136,47 +43106,47 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>63.7</v>
+        <v>2433.996</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.007307476110174255</v>
+        <v>0.1047659999767569</v>
       </c>
       <c r="AN40" s="4" t="n">
-        <v>-0.2364864864864865</v>
+        <v>-0.155781005241288</v>
       </c>
       <c r="AO40" s="4" t="n">
-        <v>-0.1210762331838565</v>
+        <v>0.2109477552387031</v>
       </c>
       <c r="AP40" s="4" t="n">
-        <v>-0.3936731107205623</v>
+        <v>0.05371039250141574</v>
       </c>
       <c r="AQ40" s="4" t="n">
-        <v>-0.4884259259259259</v>
+        <v>0.1518078638137978</v>
       </c>
       <c r="AR40" s="4" t="n">
-        <v>-0.06194690265486724</v>
+        <v>0.7279362669148413</v>
       </c>
       <c r="AS40" s="4" t="n">
-        <v>0.05357142857142838</v>
+        <v>0.3527820373094264</v>
       </c>
       <c r="AT40" s="4" t="n">
-        <v>-0.06666666666666654</v>
+        <v>0.1075019688915142</v>
       </c>
       <c r="AU40" s="4" t="n">
-        <v>0.8144796380090498</v>
+        <v>0.104516534568482</v>
       </c>
       <c r="AV40" s="4" t="n">
-        <v>1.00314465408805</v>
+        <v>-0.09215127306038395</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -43186,47 +43156,47 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>280</v>
+        <v>130.2</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.006353672649708412</v>
+        <v>0.02916646412177693</v>
       </c>
       <c r="AN41" s="4" t="n">
-        <v>0.05622489959839361</v>
+        <v>-0.1743472790185592</v>
       </c>
       <c r="AO41" s="4" t="n">
-        <v>0.01365187713310578</v>
+        <v>-0.07731685789938214</v>
       </c>
       <c r="AP41" s="4" t="n">
-        <v>0.00952380952380949</v>
+        <v>0.03343410990574447</v>
       </c>
       <c r="AQ41" s="4" t="n">
-        <v>-0.08300395256916993</v>
+        <v>-0.06715029761904767</v>
       </c>
       <c r="AR41" s="4" t="n">
-        <v>0.08365019011406849</v>
+        <v>-0.1134393751785886</v>
       </c>
       <c r="AS41" s="4" t="n">
-        <v>0.2053872053872055</v>
+        <v>0.6686435814042471</v>
       </c>
       <c r="AT41" s="4" t="n">
-        <v>0.7877358490566038</v>
+        <v>-0.9132679401135777</v>
       </c>
       <c r="AU41" s="4" t="n">
-        <v>0.3922413793103448</v>
+        <v>-0.882951146560319</v>
       </c>
       <c r="AV41" s="4" t="n">
-        <v>-0.01754385964912286</v>
+        <v>-0.8601203266007735</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -43236,47 +43206,47 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1775.139</v>
+        <v>6100</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1307222016519636</v>
+        <v>0.9842202071702864</v>
       </c>
       <c r="AN42" s="4" t="n">
-        <v>0.4315116300550919</v>
+        <v>-0.265</v>
       </c>
       <c r="AO42" s="4" t="n">
-        <v>0.351410684823863</v>
+        <v>-0.2554347826086957</v>
       </c>
       <c r="AP42" s="4" t="n">
-        <v>0.2420746141524885</v>
+        <v>-0.2787878787878788</v>
       </c>
       <c r="AQ42" s="4" t="n">
-        <v>0.007330057019968361</v>
+        <v>-0.3205128205128205</v>
       </c>
       <c r="AR42" s="4" t="n">
-        <v>-0.03846447339923531</v>
+        <v>-0.3469387755102041</v>
       </c>
       <c r="AS42" s="4" t="n">
-        <v>0.000714256047631201</v>
+        <v>-0.4087591240875912</v>
       </c>
       <c r="AT42" s="4" t="n">
-        <v>-0.1036733554766264</v>
+        <v>-0.4033613445378151</v>
       </c>
       <c r="AU42" s="4" t="n">
-        <v>-0.1621683510172314</v>
+        <v>-0.3867924528301887</v>
       </c>
       <c r="AV42" s="4" t="n">
-        <v>0.03585831501515147</v>
+        <v>-0.3645833333333334</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -43286,47 +43256,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>130.2</v>
+        <v>45.3</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.02916646412177693</v>
+        <v>0.00730904514505147</v>
       </c>
       <c r="AN43" s="4" t="n">
-        <v>-0.1743472790185592</v>
+        <v>0.2612612612612613</v>
       </c>
       <c r="AO43" s="4" t="n">
-        <v>-0.07731685789938214</v>
+        <v>0.3309438470728794</v>
       </c>
       <c r="AP43" s="4" t="n">
-        <v>0.03343410990574447</v>
-      </c>
-      <c r="AQ43" s="4" t="n">
-        <v>-0.06715029761904767</v>
+        <v>0.1210045662100458</v>
       </c>
       <c r="AR43" s="4" t="n">
-        <v>-0.1134393751785886</v>
+        <v>-0.0848214285714286</v>
       </c>
       <c r="AS43" s="4" t="n">
-        <v>0.6686435814042471</v>
+        <v>-0.3491921005385997</v>
       </c>
       <c r="AT43" s="4" t="n">
-        <v>-0.9132679401135777</v>
+        <v>-0.4725050916496946</v>
       </c>
       <c r="AU43" s="4" t="n">
-        <v>-0.882951146560319</v>
+        <v>-0.6353149955634427</v>
       </c>
       <c r="AV43" s="4" t="n">
-        <v>-0.8601203266007735</v>
+        <v>-0.5580487804878049</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -43336,38 +43303,38 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>76</v>
+        <v>2279.168</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.01226241569589209</v>
+        <v>0.09810176953249926</v>
       </c>
       <c r="AN44" s="4" t="n">
-        <v>-0.0657439446366781</v>
-      </c>
-      <c r="AO44" s="4" t="n">
-        <v>-0.06982288828337879</v>
+        <v>-0.1636600773586453</v>
       </c>
       <c r="AP44" s="4" t="n">
-        <v>-0.279750164365549</v>
+        <v>0.07526011528454424</v>
+      </c>
+      <c r="AQ44" s="4" t="n">
+        <v>0.1751889984160906</v>
       </c>
       <c r="AR44" s="4" t="n">
-        <v>-0.3787878787878788</v>
+        <v>0.8095460441351663</v>
       </c>
       <c r="AS44" s="4" t="n">
-        <v>-0.4437934822409374</v>
+        <v>0.3660370151472527</v>
       </c>
       <c r="AT44" s="4" t="n">
-        <v>-0.445002282062985</v>
+        <v>0.1228434358130872</v>
       </c>
       <c r="AU44" s="4" t="n">
-        <v>-0.5823809523809524</v>
+        <v>0.1109991345873407</v>
       </c>
       <c r="AV44" s="4" t="n">
-        <v>-0.5880758807588076</v>
+        <v>-0.1116225044240199</v>
       </c>
     </row>
     <row r="45">
@@ -43383,47 +43350,44 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>6100</v>
+        <v>76</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.9842202071702864</v>
+        <v>0.01226241569589209</v>
       </c>
       <c r="AN45" s="4" t="n">
-        <v>-0.265</v>
+        <v>-0.0657439446366781</v>
       </c>
       <c r="AO45" s="4" t="n">
-        <v>-0.2554347826086957</v>
+        <v>-0.06982288828337879</v>
       </c>
       <c r="AP45" s="4" t="n">
-        <v>-0.2787878787878788</v>
-      </c>
-      <c r="AQ45" s="4" t="n">
-        <v>-0.3205128205128205</v>
+        <v>-0.279750164365549</v>
       </c>
       <c r="AR45" s="4" t="n">
-        <v>-0.3469387755102041</v>
+        <v>-0.3787878787878788</v>
       </c>
       <c r="AS45" s="4" t="n">
-        <v>-0.4087591240875912</v>
+        <v>-0.4437934822409374</v>
       </c>
       <c r="AT45" s="4" t="n">
-        <v>-0.4033613445378151</v>
+        <v>-0.445002282062985</v>
       </c>
       <c r="AU45" s="4" t="n">
-        <v>-0.3867924528301887</v>
+        <v>-0.5823809523809524</v>
       </c>
       <c r="AV45" s="4" t="n">
-        <v>-0.3645833333333334</v>
+        <v>-0.5880758807588076</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -43437,13 +43401,43 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>173.735</v>
+        <v>51.6</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.01551366465229548</v>
+      </c>
+      <c r="AN46" s="4" t="n">
+        <v>-0.4088878020585555</v>
+      </c>
+      <c r="AO46" s="4" t="n">
+        <v>-0.4051558737557786</v>
+      </c>
+      <c r="AP46" s="4" t="n">
+        <v>-0.3955482179838091</v>
+      </c>
+      <c r="AQ46" s="4" t="n">
+        <v>-0.4134408439176694</v>
+      </c>
+      <c r="AR46" s="4" t="n">
+        <v>-0.0955246333207973</v>
+      </c>
+      <c r="AS46" s="4" t="n">
+        <v>0.05639138434895541</v>
+      </c>
+      <c r="AT46" s="4" t="n">
+        <v>0.1955532128995161</v>
+      </c>
+      <c r="AU46" s="4" t="n">
+        <v>-0.1111111111111112</v>
+      </c>
+      <c r="AV46" s="4" t="n">
+        <v>0.07276507276507282</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>MTSI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -43453,47 +43447,47 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>174.2</v>
+        <v>3.941</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.03400816039669679</v>
+        <v>0.003385814459773156</v>
       </c>
       <c r="AN47" s="4" t="n">
-        <v>0.728768926925609</v>
+        <v>0.506111111111111</v>
       </c>
       <c r="AO47" s="4" t="n">
-        <v>0.3705179282868527</v>
+        <v>0.892857142857143</v>
       </c>
       <c r="AP47" s="4" t="n">
-        <v>0.1712598425196852</v>
+        <v>-0.112062812276945</v>
       </c>
       <c r="AQ47" s="4" t="n">
-        <v>-0.1848739495798319</v>
+        <v>0.01745301112389708</v>
       </c>
       <c r="AR47" s="4" t="n">
-        <v>-0.3903274942878904</v>
+        <v>-0.03153817779417178</v>
       </c>
       <c r="AS47" s="4" t="n">
-        <v>-0.3355481727574751</v>
+        <v>0.4528301886792454</v>
       </c>
       <c r="AT47" s="4" t="n">
-        <v>-0.3151260504201681</v>
+        <v>0.3131028938906752</v>
       </c>
       <c r="AU47" s="4" t="n">
-        <v>-0.1602624179943768</v>
+        <v>-0.2158341187558906</v>
       </c>
       <c r="AV47" s="4" t="n">
-        <v>0.08806995627732661</v>
+        <v>-0.2494762902304324</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -43503,44 +43497,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>45.3</v>
+        <v>1775.139</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.00730904514505147</v>
+        <v>0.1307222016519636</v>
       </c>
       <c r="AN48" s="4" t="n">
-        <v>0.2612612612612613</v>
+        <v>0.4315116300550919</v>
       </c>
       <c r="AO48" s="4" t="n">
-        <v>0.3309438470728794</v>
+        <v>0.351410684823863</v>
       </c>
       <c r="AP48" s="4" t="n">
-        <v>0.1210045662100458</v>
+        <v>0.2420746141524885</v>
+      </c>
+      <c r="AQ48" s="4" t="n">
+        <v>0.007330057019968361</v>
       </c>
       <c r="AR48" s="4" t="n">
-        <v>-0.0848214285714286</v>
+        <v>-0.03846447339923531</v>
       </c>
       <c r="AS48" s="4" t="n">
-        <v>-0.3491921005385997</v>
+        <v>0.000714256047631201</v>
       </c>
       <c r="AT48" s="4" t="n">
-        <v>-0.4725050916496946</v>
+        <v>-0.1036733554766264</v>
       </c>
       <c r="AU48" s="4" t="n">
-        <v>-0.6353149955634427</v>
+        <v>-0.1621683510172314</v>
       </c>
       <c r="AV48" s="4" t="n">
-        <v>-0.5580487804878049</v>
+        <v>0.03585831501515147</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -43554,16 +43551,43 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>1537.028</v>
+        <v>280</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.1131875780773868</v>
+        <v>0.006353672649708412</v>
+      </c>
+      <c r="AN49" s="4" t="n">
+        <v>0.05622489959839361</v>
+      </c>
+      <c r="AO49" s="4" t="n">
+        <v>0.01365187713310578</v>
+      </c>
+      <c r="AP49" s="4" t="n">
+        <v>0.00952380952380949</v>
+      </c>
+      <c r="AQ49" s="4" t="n">
+        <v>-0.08300395256916993</v>
+      </c>
+      <c r="AR49" s="4" t="n">
+        <v>0.08365019011406849</v>
+      </c>
+      <c r="AS49" s="4" t="n">
+        <v>0.2053872053872055</v>
+      </c>
+      <c r="AT49" s="4" t="n">
+        <v>0.7877358490566038</v>
+      </c>
+      <c r="AU49" s="4" t="n">
+        <v>0.3922413793103448</v>
+      </c>
+      <c r="AV49" s="4" t="n">
+        <v>-0.01754385964912286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -43573,44 +43597,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2122.6</v>
+        <v>1537.028</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.4116757176105508</v>
-      </c>
-      <c r="AO50" s="4" t="n">
-        <v>-0.01221785048664314</v>
-      </c>
-      <c r="AP50" s="4" t="n">
-        <v>-0.0445540484997945</v>
-      </c>
-      <c r="AQ50" s="4" t="n">
-        <v>-0.1042102720978909</v>
-      </c>
-      <c r="AR50" s="4" t="n">
-        <v>0.02979979702924629</v>
-      </c>
-      <c r="AS50" s="4" t="n">
-        <v>-0.05832285115303981</v>
-      </c>
-      <c r="AT50" s="4" t="n">
-        <v>-0.07584100490406942</v>
-      </c>
-      <c r="AU50" s="4" t="n">
-        <v>-0.06924286677151192</v>
-      </c>
-      <c r="AV50" s="4" t="n">
-        <v>-0.04918473391865263</v>
+        <v>0.1131875780773868</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -43620,47 +43620,47 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>51.6</v>
+        <v>222</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.01551366465229548</v>
+        <v>0.005374651979179276</v>
       </c>
       <c r="AN51" s="4" t="n">
-        <v>-0.4088878020585555</v>
+        <v>-0.7226277372262774</v>
       </c>
       <c r="AO51" s="4" t="n">
-        <v>-0.4051558737557786</v>
+        <v>-0.5520833333333333</v>
       </c>
       <c r="AP51" s="4" t="n">
-        <v>-0.3955482179838091</v>
+        <v>-0.3795620437956204</v>
       </c>
       <c r="AQ51" s="4" t="n">
-        <v>-0.4134408439176694</v>
+        <v>-0.3451327433628318</v>
       </c>
       <c r="AR51" s="4" t="n">
-        <v>-0.0955246333207973</v>
+        <v>1.868421052631579</v>
       </c>
       <c r="AS51" s="4" t="n">
-        <v>0.05639138434895541</v>
+        <v>2.244186046511628</v>
       </c>
       <c r="AT51" s="4" t="n">
-        <v>0.1955532128995161</v>
+        <v>2.705882352941177</v>
       </c>
       <c r="AU51" s="4" t="n">
-        <v>-0.1111111111111112</v>
+        <v>2.567567567567568</v>
       </c>
       <c r="AV51" s="4" t="n">
-        <v>0.07276507276507282</v>
+        <v>0.0183486238532109</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -43670,47 +43670,47 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>3.941</v>
+        <v>63.7</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.003385814459773156</v>
+        <v>0.007307476110174255</v>
       </c>
       <c r="AN52" s="4" t="n">
-        <v>0.506111111111111</v>
+        <v>-0.2364864864864865</v>
       </c>
       <c r="AO52" s="4" t="n">
-        <v>0.892857142857143</v>
+        <v>-0.1210762331838565</v>
       </c>
       <c r="AP52" s="4" t="n">
-        <v>-0.112062812276945</v>
+        <v>-0.3936731107205623</v>
       </c>
       <c r="AQ52" s="4" t="n">
-        <v>0.01745301112389708</v>
+        <v>-0.4884259259259259</v>
       </c>
       <c r="AR52" s="4" t="n">
-        <v>-0.03153817779417178</v>
+        <v>-0.06194690265486724</v>
       </c>
       <c r="AS52" s="4" t="n">
-        <v>0.4528301886792454</v>
+        <v>0.05357142857142838</v>
       </c>
       <c r="AT52" s="4" t="n">
-        <v>0.3131028938906752</v>
+        <v>-0.06666666666666654</v>
       </c>
       <c r="AU52" s="4" t="n">
-        <v>-0.2158341187558906</v>
+        <v>0.8144796380090498</v>
       </c>
       <c r="AV52" s="4" t="n">
-        <v>-0.2494762902304324</v>
+        <v>1.00314465408805</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -43724,43 +43724,31 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2715.109</v>
+        <v>13000</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.2883363342825572</v>
-      </c>
-      <c r="AO53" s="4" t="n">
-        <v>-0.1357796518745494</v>
-      </c>
-      <c r="AP53" s="4" t="n">
-        <v>-0.1120172536091942</v>
-      </c>
-      <c r="AQ53" s="4" t="n">
-        <v>-0.1998831684329906</v>
+        <v>0.0976063909661531</v>
+      </c>
+      <c r="AC53" s="4" t="n">
+        <v>0.1384615384615384</v>
       </c>
       <c r="AR53" s="4" t="n">
-        <v>-0.03326220070052521</v>
+        <v>-0.8068783068783069</v>
       </c>
       <c r="AS53" s="4" t="n">
-        <v>0.4170634721734916</v>
-      </c>
-      <c r="AT53" s="4" t="n">
-        <v>0.5171225602689187</v>
-      </c>
-      <c r="AU53" s="4" t="n">
-        <v>0.7595545652661351</v>
+        <v>-0.8136714443219405</v>
       </c>
       <c r="AV53" s="4" t="n">
-        <v>0.646202149272413</v>
+        <v>1.89041095890411</v>
       </c>
       <c r="AW53" s="4" t="n">
-        <v>0.1432836989869608</v>
+        <v>75.92307692307692</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -43774,37 +43762,13 @@
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>10900</v>
+        <v>134000</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1.157546913836562</v>
-      </c>
-      <c r="AO54" s="4" t="n">
-        <v>0.1126760563380282</v>
-      </c>
-      <c r="AP54" s="4" t="n">
-        <v>-0.05813953488372092</v>
-      </c>
-      <c r="AQ54" s="4" t="n">
-        <v>-0.06097560975609762</v>
-      </c>
-      <c r="AR54" s="4" t="n">
-        <v>0.02531645569620244</v>
-      </c>
-      <c r="AS54" s="4" t="n">
-        <v>0.2784810126582278</v>
-      </c>
-      <c r="AT54" s="4" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="AU54" s="4" t="n">
-        <v>0.4675324675324675</v>
-      </c>
-      <c r="AV54" s="4" t="n">
-        <v>0.3580246913580247</v>
-      </c>
-      <c r="AW54" s="4" t="n">
-        <v>0.07920792079207928</v>
+        <v>1.006096645343424</v>
+      </c>
+      <c r="AB54" s="4" t="n">
+        <v>-0.6183333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -43860,7 +43824,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -43870,47 +43834,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>3200</v>
+        <v>3271</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.01056213672025851</v>
+        <v>0.1060738722962675</v>
       </c>
       <c r="AO56" s="4" t="n">
-        <v>0.8131101813110182</v>
+        <v>-0.2158993422933944</v>
       </c>
       <c r="AP56" s="4" t="n">
-        <v>0.7857142857142858</v>
+        <v>-0.04235294117647059</v>
       </c>
       <c r="AQ56" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>-0.2208452494439148</v>
       </c>
       <c r="AR56" s="4" t="n">
-        <v>0.3846153846153846</v>
+        <v>-0.04595940252776709</v>
       </c>
       <c r="AS56" s="4" t="n">
-        <v>0.4615384615384615</v>
+        <v>-0.09919766593727208</v>
       </c>
       <c r="AT56" s="4" t="n">
-        <v>0.5625</v>
+        <v>-0.09933309933309931</v>
       </c>
       <c r="AU56" s="4" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.00815660685154973</v>
       </c>
       <c r="AV56" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.03171417101565632</v>
       </c>
       <c r="AW56" s="4" t="n">
-        <v>0.6842105263157894</v>
+        <v>0.3242914979757086</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -43920,47 +43884,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>4616</v>
+        <v>10900</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.0152358822189729</v>
+        <v>1.157546913836562</v>
       </c>
       <c r="AO57" s="4" t="n">
-        <v>1.251781472684085</v>
+        <v>0.1126760563380282</v>
       </c>
       <c r="AP57" s="4" t="n">
-        <v>0.46588693957115</v>
+        <v>-0.05813953488372092</v>
       </c>
       <c r="AQ57" s="4" t="n">
-        <v>0.09554973821989532</v>
+        <v>-0.06097560975609762</v>
       </c>
       <c r="AR57" s="4" t="n">
-        <v>0.2710059171597634</v>
+        <v>0.02531645569620244</v>
       </c>
       <c r="AS57" s="4" t="n">
-        <v>0.03375527426160341</v>
+        <v>0.2784810126582278</v>
       </c>
       <c r="AT57" s="4" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="AU57" s="4" t="n">
-        <v>0.6475507765830346</v>
+        <v>0.4675324675324675</v>
       </c>
       <c r="AV57" s="4" t="n">
-        <v>0.595903165735568</v>
+        <v>0.3580246913580247</v>
       </c>
       <c r="AW57" s="4" t="n">
-        <v>3.710204081632653</v>
+        <v>0.07920792079207928</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -43970,41 +43934,41 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3271</v>
+        <v>2715.109</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.1060738722962675</v>
+        <v>0.2883363342825572</v>
       </c>
       <c r="AO58" s="4" t="n">
-        <v>-0.2158993422933944</v>
+        <v>-0.1357796518745494</v>
       </c>
       <c r="AP58" s="4" t="n">
-        <v>-0.04235294117647059</v>
+        <v>-0.1120172536091942</v>
       </c>
       <c r="AQ58" s="4" t="n">
-        <v>-0.2208452494439148</v>
+        <v>-0.1998831684329906</v>
       </c>
       <c r="AR58" s="4" t="n">
-        <v>-0.04595940252776709</v>
+        <v>-0.03326220070052521</v>
       </c>
       <c r="AS58" s="4" t="n">
-        <v>-0.09919766593727208</v>
+        <v>0.4170634721734916</v>
       </c>
       <c r="AT58" s="4" t="n">
-        <v>-0.09933309933309931</v>
+        <v>0.5171225602689187</v>
       </c>
       <c r="AU58" s="4" t="n">
-        <v>0.00815660685154973</v>
+        <v>0.7595545652661351</v>
       </c>
       <c r="AV58" s="4" t="n">
-        <v>0.03171417101565632</v>
+        <v>0.646202149272413</v>
       </c>
       <c r="AW58" s="4" t="n">
-        <v>0.3242914979757086</v>
+        <v>0.1432836989869608</v>
       </c>
     </row>
     <row r="59">
@@ -44060,7 +44024,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -44070,47 +44034,47 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>13124</v>
+        <v>4616</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.1472885616807326</v>
+        <v>0.0152358822189729</v>
       </c>
       <c r="AO60" s="4" t="n">
-        <v>3.775184275184275</v>
+        <v>1.251781472684085</v>
       </c>
       <c r="AP60" s="4" t="n">
-        <v>4.202799712849964</v>
+        <v>0.46588693957115</v>
       </c>
       <c r="AQ60" s="4" t="n">
-        <v>-0.05921946799559896</v>
+        <v>0.09554973821989532</v>
       </c>
       <c r="AR60" s="4" t="n">
-        <v>-0.1344150401149563</v>
+        <v>0.2710059171597634</v>
       </c>
       <c r="AS60" s="4" t="n">
-        <v>-0.07795214818626195</v>
+        <v>0.03375527426160341</v>
       </c>
       <c r="AT60" s="4" t="n">
-        <v>-0.1020351845463953</v>
+        <v>0.6595744680851063</v>
       </c>
       <c r="AU60" s="4" t="n">
-        <v>-0.1156439185470556</v>
+        <v>0.6475507765830346</v>
       </c>
       <c r="AV60" s="4" t="n">
-        <v>-0.01487168845541953</v>
+        <v>0.595903165735568</v>
       </c>
       <c r="AW60" s="4" t="n">
-        <v>-0.0845424107142857</v>
+        <v>3.710204081632653</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -44120,47 +44084,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>RPO (remaining performance obligation)</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>9501</v>
+        <v>3200</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.1066282097324475</v>
+        <v>0.01056213672025851</v>
       </c>
       <c r="AO61" s="4" t="n">
-        <v>2.328459707582455</v>
+        <v>0.8131101813110182</v>
       </c>
       <c r="AP61" s="4" t="n">
-        <v>2.777643747486932</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="AQ61" s="4" t="n">
-        <v>0.03283644323986246</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AR61" s="4" t="n">
-        <v>-0.02053427131856644</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AS61" s="4" t="n">
-        <v>0.05271222801103281</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="AT61" s="4" t="n">
-        <v>0.00787653006918565</v>
+        <v>0.5625</v>
       </c>
       <c r="AU61" s="4" t="n">
-        <v>-0.07266855066612843</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="AV61" s="4" t="n">
-        <v>-0.02572066388430549</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AW61" s="4" t="n">
-        <v>-0.07802037845705967</v>
+        <v>0.6842105263157894</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -44170,47 +44134,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RPO (remaining performance obligation)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>179200</v>
+        <v>6412</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2.011133057999641</v>
+        <v>0.02116388145321799</v>
       </c>
       <c r="AO62" s="4" t="n">
-        <v>-0.009345794392523366</v>
+        <v>1.360768175582991</v>
       </c>
       <c r="AP62" s="4" t="n">
-        <v>0.009852216748768461</v>
+        <v>0.6897654584221748</v>
       </c>
       <c r="AQ62" s="4" t="n">
-        <v>-0.1913357400722022</v>
+        <v>0.3560209424083769</v>
       </c>
       <c r="AR62" s="4" t="n">
-        <v>0.07860262008733621</v>
+        <v>0.34151065203357</v>
       </c>
       <c r="AS62" s="4" t="n">
-        <v>0.2971698113207548</v>
+        <v>0.1824520627542128</v>
       </c>
       <c r="AT62" s="4" t="n">
-        <v>0.6243902439024391</v>
+        <v>0.522397476340694</v>
       </c>
       <c r="AU62" s="4" t="n">
-        <v>1.008928571428572</v>
+        <v>0.4186431329288471</v>
       </c>
       <c r="AV62" s="4" t="n">
-        <v>5.663967611336032</v>
+        <v>0.5</v>
       </c>
       <c r="AW62" s="4" t="n">
-        <v>5.516363636363637</v>
+        <v>2.150859950859951</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -44220,35 +44184,47 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>13000</v>
+        <v>9501</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.0976063909661531</v>
-      </c>
-      <c r="AC63" s="4" t="n">
-        <v>0.1384615384615384</v>
+        <v>0.1066282097324475</v>
+      </c>
+      <c r="AO63" s="4" t="n">
+        <v>2.328459707582455</v>
+      </c>
+      <c r="AP63" s="4" t="n">
+        <v>2.777643747486932</v>
+      </c>
+      <c r="AQ63" s="4" t="n">
+        <v>0.03283644323986246</v>
       </c>
       <c r="AR63" s="4" t="n">
-        <v>-0.8068783068783069</v>
+        <v>-0.02053427131856644</v>
       </c>
       <c r="AS63" s="4" t="n">
-        <v>-0.8136714443219405</v>
+        <v>0.05271222801103281</v>
+      </c>
+      <c r="AT63" s="4" t="n">
+        <v>0.00787653006918565</v>
+      </c>
+      <c r="AU63" s="4" t="n">
+        <v>-0.07266855066612843</v>
       </c>
       <c r="AV63" s="4" t="n">
-        <v>1.89041095890411</v>
+        <v>-0.02572066388430549</v>
       </c>
       <c r="AW63" s="4" t="n">
-        <v>75.92307692307692</v>
+        <v>-0.07802037845705967</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -44262,43 +44238,43 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>6412</v>
+        <v>13124</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.02116388145321799</v>
+        <v>0.1472885616807326</v>
       </c>
       <c r="AO64" s="4" t="n">
-        <v>1.360768175582991</v>
+        <v>3.775184275184275</v>
       </c>
       <c r="AP64" s="4" t="n">
-        <v>0.6897654584221748</v>
+        <v>4.202799712849964</v>
       </c>
       <c r="AQ64" s="4" t="n">
-        <v>0.3560209424083769</v>
+        <v>-0.05921946799559896</v>
       </c>
       <c r="AR64" s="4" t="n">
-        <v>0.34151065203357</v>
+        <v>-0.1344150401149563</v>
       </c>
       <c r="AS64" s="4" t="n">
-        <v>0.1824520627542128</v>
+        <v>-0.07795214818626195</v>
       </c>
       <c r="AT64" s="4" t="n">
-        <v>0.522397476340694</v>
+        <v>-0.1020351845463953</v>
       </c>
       <c r="AU64" s="4" t="n">
-        <v>0.4186431329288471</v>
+        <v>-0.1156439185470556</v>
       </c>
       <c r="AV64" s="4" t="n">
-        <v>0.5</v>
+        <v>-0.01487168845541953</v>
       </c>
       <c r="AW64" s="4" t="n">
-        <v>2.150859950859951</v>
+        <v>-0.0845424107142857</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -44312,13 +44288,37 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>134000</v>
+        <v>179200</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1.006096645343424</v>
-      </c>
-      <c r="AB65" s="4" t="n">
-        <v>-0.6183333333333334</v>
+        <v>2.011133057999641</v>
+      </c>
+      <c r="AO65" s="4" t="n">
+        <v>-0.009345794392523366</v>
+      </c>
+      <c r="AP65" s="4" t="n">
+        <v>0.009852216748768461</v>
+      </c>
+      <c r="AQ65" s="4" t="n">
+        <v>-0.1913357400722022</v>
+      </c>
+      <c r="AR65" s="4" t="n">
+        <v>0.07860262008733621</v>
+      </c>
+      <c r="AS65" s="4" t="n">
+        <v>0.2971698113207548</v>
+      </c>
+      <c r="AT65" s="4" t="n">
+        <v>0.6243902439024391</v>
+      </c>
+      <c r="AU65" s="4" t="n">
+        <v>1.008928571428572</v>
+      </c>
+      <c r="AV65" s="4" t="n">
+        <v>5.663967611336032</v>
+      </c>
+      <c r="AW65" s="4" t="n">
+        <v>5.516363636363637</v>
       </c>
     </row>
   </sheetData>
@@ -44834,7 +44834,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -44864,7 +44864,7 @@
         <v>0.1060738722962675</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="M14" s="5" t="b">
         <v>0</v>
@@ -44883,7 +44883,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -44913,7 +44913,7 @@
         <v>0.1060738722962675</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M15" s="5" t="b">
         <v>0</v>
@@ -45662,12 +45662,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -45697,7 +45697,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="M31" s="5" t="b">
         <v>0</v>
@@ -45711,12 +45711,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -45746,7 +45746,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="M32" s="5" t="b">
         <v>0</v>
@@ -45956,12 +45956,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TOTAL COMPANY</t>
+          <t>Reportable</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -45991,7 +45991,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M37" s="5" t="b">
         <v>0</v>
@@ -46005,12 +46005,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reportable</t>
+          <t>TOTAL COMPANY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -46040,7 +46040,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M38" s="5" t="b">
         <v>0</v>
@@ -47176,7 +47176,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contract liabilities (total)</t>
+          <t>Contract liabilities (current)</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -47223,7 +47223,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contract liabilities (current)</t>
+          <t>Contract liabilities (total)</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
